--- a/Prueba_01.xlsx
+++ b/Prueba_01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desarrollo\presupuesto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA022EE9-C510-4F68-9879-652E868E83FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F93A8D9-5026-47DC-B95F-79D20C8511BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{61D2474A-68BD-4267-882F-28F76628F992}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{803325BB-F87B-404C-9CC4-32E0805D7043}"/>
   </bookViews>
   <sheets>
     <sheet name="INSUMOS" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,42 @@
     <sheet name="APU" sheetId="3" r:id="rId3"/>
     <sheet name="PRESUPUESTO" sheetId="4" r:id="rId4"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="ACTIVIDADES" localSheetId="2">[1]!T_act[DESCRIPCIÓN]</definedName>
+    <definedName name="ACTIVIDADES" localSheetId="1">[1]!T_act[DESCRIPCIÓN]</definedName>
+    <definedName name="ACTIVIDADES" localSheetId="3">[1]!T_act[DESCRIPCIÓN]</definedName>
+    <definedName name="ACTIVIDADES">#REF!</definedName>
+    <definedName name="BÁSICOS">[1]!T_basico[DESCRIPCIÓN]</definedName>
+    <definedName name="BD_APUS">[1]!T_apus[DESCRIPCIÓN]</definedName>
+    <definedName name="BD_APUS_B">[1]!T_basico[DESCRIPCIÓN]</definedName>
+    <definedName name="EQUIPOS" localSheetId="2">[1]!T_equipos[DESCRIPCIÓN]</definedName>
+    <definedName name="EQUIPOS" localSheetId="1">[1]!T_equipos[DESCRIPCIÓN]</definedName>
+    <definedName name="EQUIPOS" localSheetId="3">[1]!T_equipos[DESCRIPCIÓN]</definedName>
+    <definedName name="EQUIPOS">#REF!</definedName>
+    <definedName name="MANO_DE_OBRA" localSheetId="2">[1]!T_mano[DESCRIPCIÓN]</definedName>
+    <definedName name="MANO_DE_OBRA" localSheetId="1">[1]!T_mano[DESCRIPCIÓN]</definedName>
+    <definedName name="MANO_DE_OBRA" localSheetId="3">[1]!T_mano[DESCRIPCIÓN]</definedName>
+    <definedName name="MANO_DE_OBRA">#REF!</definedName>
+    <definedName name="MATERIALES" localSheetId="2">[1]!T_mat[DESCRIPCIÓN]</definedName>
+    <definedName name="MATERIALES" localSheetId="1">[1]!T_mat[DESCRIPCIÓN]</definedName>
+    <definedName name="MATERIALES" localSheetId="3">[1]!T_mat[DESCRIPCIÓN]</definedName>
+    <definedName name="MATERIALES">#REF!</definedName>
+    <definedName name="OTROS" localSheetId="2">[1]!T_otros[DESCRIPCIÓN]</definedName>
+    <definedName name="OTROS" localSheetId="1">[1]!T_otros[DESCRIPCIÓN]</definedName>
+    <definedName name="OTROS" localSheetId="3">[1]!T_otros[DESCRIPCIÓN]</definedName>
+    <definedName name="OTROS">#REF!</definedName>
+    <definedName name="SUBCONTRATOS" localSheetId="2">[1]!T_sub[DESCRIPCIÓN]</definedName>
+    <definedName name="SUBCONTRATOS" localSheetId="1">[1]!T_sub[DESCRIPCIÓN]</definedName>
+    <definedName name="SUBCONTRATOS" localSheetId="3">[1]!T_sub[DESCRIPCIÓN]</definedName>
+    <definedName name="SUBCONTRATOS">#REF!</definedName>
+    <definedName name="TRANSPORTE" localSheetId="2">[1]!T_trans[DESCRIPCIÓN]</definedName>
+    <definedName name="TRANSPORTE" localSheetId="1">[1]!T_trans[DESCRIPCIÓN]</definedName>
+    <definedName name="TRANSPORTE" localSheetId="3">[1]!T_trans[DESCRIPCIÓN]</definedName>
+    <definedName name="TRANSPORTE">#REF!</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="57">
   <si>
     <t>INSUMOS</t>
   </si>
@@ -78,22 +114,49 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t xml:space="preserve">agua </t>
+    <t>acero corru.fig 1/4-1" 60000 psi</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>herramienta menor</t>
+  </si>
+  <si>
+    <t>gl</t>
+  </si>
+  <si>
+    <t>cuadrilla AA albañileria</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>agua</t>
   </si>
   <si>
     <t>lt</t>
   </si>
   <si>
-    <t>cemento</t>
+    <t>concretadora trompo 3 sacos</t>
   </si>
   <si>
-    <t>kg</t>
+    <t>d</t>
   </si>
   <si>
-    <t>arena</t>
+    <t>alambre negro recocido c-17</t>
+  </si>
+  <si>
+    <t>arena lavada de peña</t>
   </si>
   <si>
     <t>m3</t>
+  </si>
+  <si>
+    <t>cemento gris</t>
+  </si>
+  <si>
+    <t>grava 1"</t>
   </si>
   <si>
     <t>ANALISIS DE PRECIOS UNITARIOS BÁSICOS</t>
@@ -102,7 +165,7 @@
     <t>CÓD</t>
   </si>
   <si>
-    <t>basico 01</t>
+    <t>NOMBRE A.P.U. BÁSICO</t>
   </si>
   <si>
     <t>UND</t>
@@ -123,10 +186,16 @@
     <t>Total</t>
   </si>
   <si>
+    <t>Basico 01</t>
+  </si>
+  <si>
     <t xml:space="preserve">ANALISIS DE PRECIOS UNITARIOS </t>
   </si>
   <si>
-    <t>Apu de prueba 01</t>
+    <t>Apu 01</t>
+  </si>
+  <si>
+    <t>Apu 02</t>
   </si>
   <si>
     <t>APU BÁSICOS</t>
@@ -135,10 +204,16 @@
     <t>PRESUPUESTO</t>
   </si>
   <si>
-    <t>CAPÍTULO</t>
+    <t>CAPÍTULO 1</t>
   </si>
   <si>
     <t>COSTO</t>
+  </si>
+  <si>
+    <t>CAPÍTULO 2</t>
+  </si>
+  <si>
+    <t>CAPÍTULO</t>
   </si>
   <si>
     <t>PORCENTAJE</t>
@@ -148,6 +223,9 @@
   </si>
   <si>
     <t>TOTAL DIRECTOS</t>
+  </si>
+  <si>
+    <t>OK</t>
   </si>
   <si>
     <t>ADMINISTRACIÓN (A)</t>
@@ -176,7 +254,7 @@
     <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;-&quot;\ _€_-;_-@_-"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -229,12 +307,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -248,7 +320,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -261,8 +333,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66FF66"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="21">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -443,6 +521,62 @@
     </border>
     <border>
       <left style="medium">
+        <color rgb="FF00A4F3"/>
+      </left>
+      <right style="hair">
+        <color rgb="FF00A4F3"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF00A4F3"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF00A4F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="FF00A4F3"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF00A4F3"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF00A4F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color rgb="FF00A4F3"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF00A4F3"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF00A4F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="FF00A4F3"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF00A4F3"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF00A4F3"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF00A4F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color rgb="FF009999"/>
       </left>
       <right/>
@@ -532,6 +666,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF009999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -589,63 +732,71 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="41" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="41" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="41" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -654,540 +805,51 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="41" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="41" fontId="7" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 12 3" xfId="3" xr:uid="{560DB3BF-889F-4F29-A7B3-6D394924CB54}"/>
-    <cellStyle name="Normal 41" xfId="2" xr:uid="{A6211BBE-3762-4A1D-A361-07114006ACB2}"/>
+    <cellStyle name="Normal 12 3" xfId="3" xr:uid="{548129DB-985F-4177-8030-E9FE96AFF519}"/>
+    <cellStyle name="Normal 41" xfId="2" xr:uid="{AA1D3391-830E-4BD4-AB6A-281ECB55126A}"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="91">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <font>
         <strike val="0"/>
@@ -1232,237 +894,6 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <color theme="0"/>
@@ -1504,149 +935,6 @@
           <color rgb="FF00AC56"/>
         </horizontal>
       </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="33" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1693,17 +981,17 @@
     </dxf>
   </dxfs>
   <tableStyles count="3" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="S5S Blue" pivot="0" count="2" xr9:uid="{F7046CAD-0AE3-4D55-9702-CC00D0E4D355}">
-      <tableStyleElement type="wholeTable" dxfId="90"/>
-      <tableStyleElement type="headerRow" dxfId="89"/>
+    <tableStyle name="S5S Blue" pivot="0" count="2" xr9:uid="{DF5AF5E1-D628-44F0-9561-EC674D185928}">
+      <tableStyleElement type="wholeTable" dxfId="5"/>
+      <tableStyleElement type="headerRow" dxfId="4"/>
     </tableStyle>
-    <tableStyle name="S5S Green" pivot="0" count="2" xr9:uid="{C604B011-10C7-4B1F-96A8-46B7556473FC}">
-      <tableStyleElement type="wholeTable" dxfId="53"/>
-      <tableStyleElement type="headerRow" dxfId="52"/>
+    <tableStyle name="S5S Green" pivot="0" count="2" xr9:uid="{011D91F5-5771-4BDE-A7CE-D18488AD601B}">
+      <tableStyleElement type="wholeTable" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
     </tableStyle>
-    <tableStyle name="S5S Greenblue" pivot="0" count="2" xr9:uid="{14236D0D-4E3D-44F6-80DC-FB4E48C07D6A}">
-      <tableStyleElement type="wholeTable" dxfId="29"/>
-      <tableStyleElement type="headerRow" dxfId="28"/>
+    <tableStyle name="S5S Greenblue" pivot="0" count="2" xr9:uid="{474D4F8A-5130-4403-923D-A3BB2AEE46BD}">
+      <tableStyleElement type="wholeTable" dxfId="1"/>
+      <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1717,241 +1005,1596 @@
 </styleSheet>
 </file>
 
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6B166161-6912-4AEA-BC4B-BEB96455E41C}" name="T_mat" displayName="T_mat" ref="A4:E10" totalsRowShown="0" headerRowDxfId="88">
-  <autoFilter ref="A4:E10" xr:uid="{B4D06BE8-5310-4331-9C36-28CE19835CAF}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:E88">
-    <sortCondition ref="A3:A87"/>
-  </sortState>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{A9E27C12-8F5A-43A1-8685-AAB7C43B61BB}" name="DESCRIPCIÓN" dataDxfId="87"/>
-    <tableColumn id="2" xr3:uid="{99324B33-77BD-443D-A682-C95B7C523B2D}" name="CÓDIGO" dataDxfId="86"/>
-    <tableColumn id="3" xr3:uid="{357777AF-87FD-407C-AEBD-DB9525DF3BBA}" name="UNIDAD" dataDxfId="85"/>
-    <tableColumn id="4" xr3:uid="{E3872A6B-B0CE-425F-9A76-30ACB350225A}" name="PRECIO" dataDxfId="84"/>
-    <tableColumn id="5" xr3:uid="{CAA0D48A-A769-4D4A-93D6-E0816A794C00}" name="FECHA"/>
-  </tableColumns>
-  <tableStyleInfo name="S5S Blue" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>52917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740833</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>338667</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Elipse 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{166874B5-49D6-48BA-8672-EAE1FE822ECF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="444500" y="52917"/>
+          <a:ext cx="296333" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="800" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0066FF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>52917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740833</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>338667</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Elipse 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9491C37B-CEE6-44D5-8CA4-2442E6429BB2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="444500" y="52917"/>
+          <a:ext cx="296333" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="800" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0066FF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>52917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740833</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>338667</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Elipse 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B71A6E1-4D79-4BC3-BF7C-6F4F85298CC1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="444500" y="52917"/>
+          <a:ext cx="296333" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="800" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0066FF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>52917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740833</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>338667</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Elipse 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A431070-F839-4E03-9199-CC0F465B8DA3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="444500" y="52917"/>
+          <a:ext cx="296333" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="800" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0066FF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>52917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740833</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>338667</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Elipse 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBF5ACCA-53E2-4987-BAA3-F077A9D79227}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="444500" y="52917"/>
+          <a:ext cx="296333" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="800" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0066FF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>52917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740833</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>338667</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Elipse 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD3BD931-0E06-40AD-8192-00703D0B1AAD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="444500" y="52917"/>
+          <a:ext cx="296333" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="800" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0066FF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>52917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740833</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>338667</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Elipse 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BB64923-E71E-4B41-839A-6F4E372325B1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="444500" y="52917"/>
+          <a:ext cx="296333" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="800" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0066FF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>52917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740833</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>338667</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Elipse 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E2648EA-0B92-4627-898C-5FF0EB2E88C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="444500" y="52917"/>
+          <a:ext cx="296333" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="800" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0066FF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>52917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740833</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>338667</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Elipse 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F876F5EA-FA8D-46B5-81FF-A76BE983DF2B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="444500" y="52917"/>
+          <a:ext cx="296333" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="800" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0066FF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>52917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740833</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>338667</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Elipse 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8B5BAD3-0E63-41AF-BEA4-AD71CDAB1D07}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="444500" y="52917"/>
+          <a:ext cx="296333" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="800" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0066FF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>52917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740833</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>338667</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Elipse 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69B75225-EF31-4D58-9029-4E23F27DBE09}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="444500" y="52917"/>
+          <a:ext cx="296333" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="800" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0066FF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>52917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740833</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>338667</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Elipse 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B71AE742-C61F-494C-BC2E-6F184E004333}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="444500" y="52917"/>
+          <a:ext cx="296333" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="800" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0066FF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>52917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740833</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>338667</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Elipse 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC737551-8E43-42E8-AE44-7A00A7FB392A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="444500" y="52917"/>
+          <a:ext cx="296333" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="800" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0066FF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>52917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740833</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>338667</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Elipse 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3172DA40-2E0B-47DD-865D-B6DBCDCC733C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="444500" y="52917"/>
+          <a:ext cx="296333" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="800" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0066FF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>52917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740833</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>338667</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="Elipse 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E18F245B-F328-412E-9A5C-F8221ADE3103}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="444500" y="52917"/>
+          <a:ext cx="296333" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="800" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0066FF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>52917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740833</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>338667</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="Elipse 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07A39E99-263C-4107-B09A-31F0C5298EEF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="444500" y="52917"/>
+          <a:ext cx="296333" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="800" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0066FF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>52917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740833</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>338667</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="Elipse 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34C1FDB8-D454-4B50-9304-885DA4A9E164}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="444500" y="52917"/>
+          <a:ext cx="296333" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="800" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0066FF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>52917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740833</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>338667</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="Elipse 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22A03A45-96BE-4D62-9B06-8E33978BDD47}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="444500" y="52917"/>
+          <a:ext cx="296333" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="800" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0066FF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>52917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740833</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>338667</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="Elipse 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93CE6DB1-79F8-4854-AE23-38C0B3D2A9ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="444500" y="52917"/>
+          <a:ext cx="296333" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="800" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0066FF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>52917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740833</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>338667</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="Elipse 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C28D7F6-B00B-42C9-9B49-5EC9A788227A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="444500" y="52917"/>
+          <a:ext cx="296333" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="800" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0066FF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>52917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740833</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>338667</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="Elipse 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07C327B0-613D-4B4C-B8DC-88D5A8F65AAC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="444500" y="52917"/>
+          <a:ext cx="296333" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="800" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0066FF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>52917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740833</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>338667</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="Elipse 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DDE2840-2D28-46DD-A0FC-D0CA57DE8797}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="444500" y="52917"/>
+          <a:ext cx="296333" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="800" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0066FF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>52917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740833</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>338667</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="Elipse 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2B733E0-2387-482C-A514-76DBB1884508}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="444500" y="52917"/>
+          <a:ext cx="296333" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="800" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0066FF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>52917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740833</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>338667</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="Elipse 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FB77960-3AA4-4F96-B247-5FC4BCCCC4A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="444500" y="52917"/>
+          <a:ext cx="296333" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent3">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="800" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0066FF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
-<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{A060DAD0-CAE7-4EAF-93A9-1552B5067534}" name="Tabla7" displayName="Tabla7" ref="B4:H10" totalsRowCount="1" headerRowDxfId="27" dataDxfId="26" totalsRowDxfId="25">
-  <autoFilter ref="B4:H9" xr:uid="{3083C817-4351-4ACD-B60B-670E444CA557}">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-    <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
-    <filterColumn colId="6" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{BB55B8C0-AA01-4218-A380-AF0508EA94FC}" name="CÓDIGO" totalsRowLabel="Total" dataDxfId="23" totalsRowDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{1AC342F9-9F80-4AF0-B11D-5539D8B6BE06}" name="DESCRIPCIÓN" dataDxfId="21" totalsRowDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{4B6D374B-7360-4ECD-A023-53AC180B6225}" name="UNIDAD" dataDxfId="19" totalsRowDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{A6E0C932-6FA5-4789-9E76-524E5173A402}" name="FACTOR" dataDxfId="17" totalsRowDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{69470EE9-981C-46D6-9CB6-7022BEF1CB3C}" name="CANTIDAD" dataDxfId="15" totalsRowDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{5428D6DD-DE97-457E-973B-D45DD6FE2944}" name="COSTO" dataDxfId="13" totalsRowDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{A3BF9822-CE4C-4F42-A78B-B750902FD973}" name="TOTAL" totalsRowFunction="custom" dataDxfId="11" totalsRowDxfId="12">
-      <calculatedColumnFormula>Tabla7[[#This Row],[FACTOR]]*Tabla7[[#This Row],[CANTIDAD]]*Tabla7[[#This Row],[COSTO]]</calculatedColumnFormula>
-      <totalsRowFormula>SUM(Tabla7[TOTAL])</totalsRowFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="S5S Greenblue" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{308A9A6E-79AE-45A8-87C3-732360ED4C80}" name="Tabla12" displayName="Tabla12" ref="B14:E18" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="B14:E18" xr:uid="{AC21817C-2844-435B-AA60-0EB0910C5F94}">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{9DD5A783-A708-4D46-B220-213EE8BEFE38}" name="CÓD" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{0E4B1707-938C-4DCE-977B-2DB022DB5C5C}" name="CAPÍTULO" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{039CB716-2DFD-466B-94B9-BE3048D7FF7E}" name="PORCENTAJE" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{314602AE-2B34-4390-AD7F-E6C7870042C5}" name="SUBTOTAL" dataDxfId="5"/>
-  </tableColumns>
-  <tableStyleInfo name="S5S Greenblue" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{DBD5CE2E-5431-4791-B403-D7B99DEA2704}" name="Tabla13" displayName="Tabla13" ref="C21:E28" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="C21:E28" xr:uid="{EAB7FFF4-6756-45E1-A3C4-C3ECC007B0D6}">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{FC168BA8-5A41-4165-9061-FCBEA05F3013}" name="DESCRIPCIÓN" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{23CDE258-3F95-41A1-902E-FF6DE21BAA8B}" name="PORCENTAJE" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{27714894-C486-49AE-ADFA-F08994B529F1}" name="SUBTOTAL" dataDxfId="0"/>
-  </tableColumns>
-  <tableStyleInfo name="S5S Greenblue" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D59583AC-B326-4802-8C94-81DAE484A132}" name="T_equipos" displayName="T_equipos" ref="G4:K11" totalsRowShown="0" headerRowDxfId="83">
-  <autoFilter ref="G4:K11" xr:uid="{93BDFE09-8CE9-473D-9D94-77B3E6C41C97}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{EFCA19A9-818A-4A86-9C57-EE33735A3D30}" name="DESCRIPCIÓN" dataDxfId="82"/>
-    <tableColumn id="2" xr3:uid="{B6025D84-2DFF-4EC1-9ADA-050634FD1371}" name="CÓDIGO" dataDxfId="81"/>
-    <tableColumn id="3" xr3:uid="{284057EA-A5FA-4516-9BC9-844717FD5E16}" name="UNIDAD" dataDxfId="80"/>
-    <tableColumn id="4" xr3:uid="{4915C0A5-E4E0-4B11-BC8D-5FF3A1730658}" name="PRECIO" dataDxfId="79"/>
-    <tableColumn id="5" xr3:uid="{D9D92621-7F8B-45FD-930D-E8A98ED7DE00}" name="FECHA"/>
-  </tableColumns>
-  <tableStyleInfo name="S5S Blue" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{73AD0532-558A-49DC-8D05-A8DFD438C8B8}" name="T_mano" displayName="T_mano" ref="M4:Q11" totalsRowShown="0" headerRowDxfId="78">
-  <autoFilter ref="M4:Q11" xr:uid="{3B30CF46-3348-4BC3-8367-F27EFBF67E03}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="M5:Q19">
-    <sortCondition ref="N4"/>
-  </sortState>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{5CD29DDA-144C-49C7-BEEC-2D38A35A1416}" name="DESCRIPCIÓN" dataDxfId="77"/>
-    <tableColumn id="2" xr3:uid="{8901863D-993B-463D-9819-8C6A0FCA041F}" name="CÓDIGO" dataDxfId="76"/>
-    <tableColumn id="3" xr3:uid="{817AD4CE-4464-4554-B04C-B58B0E4BFB89}" name="UNIDAD" dataDxfId="75"/>
-    <tableColumn id="4" xr3:uid="{9030DD22-A35F-4ED4-B68D-E0D657D29F43}" name="PRECIO" dataDxfId="74"/>
-    <tableColumn id="5" xr3:uid="{D5541ABC-2B2E-457B-9896-42E4D9B0054A}" name="FECHA"/>
-  </tableColumns>
-  <tableStyleInfo name="S5S Blue" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A9A13C93-3F5A-4178-A488-E76AD1FDEBA4}" name="T_trans" displayName="T_trans" ref="S4:W11" totalsRowShown="0" headerRowDxfId="73">
-  <autoFilter ref="S4:W11" xr:uid="{643F9E8E-4E92-4BD0-8DC6-CA38804D426A}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="S5:W15">
-    <sortCondition ref="T4:T15"/>
-  </sortState>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{A66623C0-6CAD-45EA-BFCE-9ACB12BD27AC}" name="DESCRIPCIÓN" dataDxfId="72"/>
-    <tableColumn id="2" xr3:uid="{DD261B6A-DBED-439E-856E-3713C8885623}" name="CÓDIGO" dataDxfId="71"/>
-    <tableColumn id="3" xr3:uid="{253BBA77-70F1-4003-BA02-B931D0CC80A3}" name="UNIDAD" dataDxfId="70"/>
-    <tableColumn id="4" xr3:uid="{18D353AA-5DBC-4B28-9165-D3C861D7D581}" name="PRECIO" dataDxfId="69"/>
-    <tableColumn id="5" xr3:uid="{3E8FAC13-5AE2-4B8E-A922-2C643075ADFE}" name="FECHA"/>
-  </tableColumns>
-  <tableStyleInfo name="S5S Blue" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{34A2FBFD-7591-46E1-8A52-C75F704D023F}" name="T_sub" displayName="T_sub" ref="Y4:AC11" totalsRowShown="0" headerRowDxfId="68">
-  <autoFilter ref="Y4:AC11" xr:uid="{59205A9C-EAB5-4F68-8899-7FB788B37E57}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="Y5:AC18">
-    <sortCondition ref="Z4"/>
-  </sortState>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{FE00967A-6BD8-45CB-9A56-4B248114DA38}" name="DESCRIPCIÓN" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{0C27EB65-71DE-4D80-938A-71A9EDBE1D45}" name="CÓDIGO" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{272625A7-49CB-48C4-9625-F93787E0A067}" name="UNIDAD" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{0AA72B1A-732B-43CE-AC98-56FC8A112106}" name="PRECIO" dataDxfId="64"/>
-    <tableColumn id="5" xr3:uid="{E61A3BB7-AFB3-460F-AD1D-07658BA44A7E}" name="FECHA"/>
-  </tableColumns>
-  <tableStyleInfo name="S5S Blue" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EEBE3974-F54D-48A3-8731-A4E4F0210B5C}" name="T_otros" displayName="T_otros" ref="AK4:AO11" totalsRowShown="0" headerRowDxfId="63">
-  <autoFilter ref="AK4:AO11" xr:uid="{C737E907-FE65-4BD6-95F0-40FA848B029A}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="AK5:AO18">
-    <sortCondition ref="AL4"/>
-  </sortState>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{97276B1E-3AE6-4BDE-963D-FD96ED5930B1}" name="DESCRIPCIÓN" dataDxfId="62"/>
-    <tableColumn id="2" xr3:uid="{FDF42031-62F2-42BC-ADD9-BDE566E8D0F0}" name="CÓDIGO" dataDxfId="61"/>
-    <tableColumn id="3" xr3:uid="{F12B7F64-8B4A-43BF-AA25-F524947FA310}" name="UNIDAD" dataDxfId="60"/>
-    <tableColumn id="4" xr3:uid="{691FBF68-E727-444B-A24E-153039C18F2A}" name="PRECIO" dataDxfId="59"/>
-    <tableColumn id="5" xr3:uid="{3A14DC27-9F61-4624-8EBE-15871B7E3112}" name="FECHA"/>
-  </tableColumns>
-  <tableStyleInfo name="S5S Blue" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{0F27D683-8612-4607-897D-2C1CE9617940}" name="T_act" displayName="T_act" ref="AE4:AI11" totalsRowShown="0" headerRowDxfId="58">
-  <autoFilter ref="AE4:AI11" xr:uid="{5F0F9734-FB6B-4020-86F9-C17EB0CA5E0E}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="AE5:AI15">
-    <sortCondition ref="AE4:AE15"/>
-  </sortState>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{46A59D89-F5DD-4A61-A180-7DFD8001DAFC}" name="DESCRIPCIÓN" dataDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{8D00AB0D-00CF-4B77-AE3B-4A1163E1D151}" name="CÓDIGO" dataDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{B3F0BCE6-523B-46B3-9F3E-626BFABA804F}" name="UNIDAD" dataDxfId="55"/>
-    <tableColumn id="4" xr3:uid="{B37BDD8C-2426-4F1C-AD76-4E4179969F57}" name="PRECIO" dataDxfId="54"/>
-    <tableColumn id="5" xr3:uid="{43B94023-15C2-4FF7-A28E-2753B69DBB9C}" name="FECHA"/>
-  </tableColumns>
-  <tableStyleInfo name="S5S Blue" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{E9C4EA82-9D64-427C-9C48-39F0A14184D4}" name="Tabla3" displayName="Tabla3" ref="A4:H10" totalsRowCount="1" headerRowDxfId="51">
-  <autoFilter ref="A4:H9" xr:uid="{E14AF057-549A-4F77-947F-28E8505B0740}">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-    <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
-    <filterColumn colId="6" hiddenButton="1"/>
-    <filterColumn colId="7" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C483856F-5BE4-493C-AD2E-B5E9CB5649CF}" name="TIPO" totalsRowLabel="Total" totalsRowDxfId="50"/>
-    <tableColumn id="2" xr3:uid="{28DB8DC8-6925-47FA-900F-D066378C5812}" name="CÓDIGO"/>
-    <tableColumn id="3" xr3:uid="{17519A96-D423-47DF-932F-E92B256158DC}" name="DESCRIPCIÓN"/>
-    <tableColumn id="4" xr3:uid="{105091DE-E54A-4964-A295-17FCF88D93EC}" name="UNIDAD" dataDxfId="49"/>
-    <tableColumn id="5" xr3:uid="{A6C6DBA9-F94B-465C-B3FE-31832013879A}" name="FACTOR" dataDxfId="48">
-      <calculatedColumnFormula>1</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="6" xr3:uid="{8B3D1A7D-1FFE-4D1F-85D6-CF306FA08282}" name="CANTIDAD" dataDxfId="47"/>
-    <tableColumn id="7" xr3:uid="{DDE8A1A1-FB68-47B8-9E18-900543E1BE43}" name="PRECIO" dataDxfId="45" totalsRowDxfId="46"/>
-    <tableColumn id="8" xr3:uid="{737BBB3B-ECF8-4066-BD94-9E5EFDA8B488}" name="TOTAL" totalsRowFunction="custom" dataDxfId="43" totalsRowDxfId="44">
-      <calculatedColumnFormula>Tabla3[[#This Row],[CANTIDAD]]*Tabla3[[#This Row],[PRECIO]]*Tabla3[[#This Row],[FACTOR]]</calculatedColumnFormula>
-      <totalsRowFormula>SUM(Tabla3[TOTAL])</totalsRowFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="S5S Green" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{6888FDB4-26EA-42C4-8F1A-B75F46AAF7C5}" name="Tabla5" displayName="Tabla5" ref="A4:G8" totalsRowCount="1" headerRowDxfId="42" headerRowCellStyle="Normal 41" dataCellStyle="Normal 41">
-  <autoFilter ref="A4:G7" xr:uid="{3FEB5D29-012E-45DD-B783-195C12069059}">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-    <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
-    <filterColumn colId="6" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{CB893947-50D0-470F-BC09-A1D12464B7B2}" name="TIPO" totalsRowLabel="Total" totalsRowDxfId="41" dataCellStyle="Normal 41"/>
-    <tableColumn id="2" xr3:uid="{AC018D28-63AF-4C21-8CDB-D5C21455BCB5}" name="CÓDIGO" totalsRowDxfId="40" dataCellStyle="Normal 12 3"/>
-    <tableColumn id="4" xr3:uid="{CD318D8C-8619-4CC9-9717-B4AC709C23AB}" name="UNIDAD" dataDxfId="38" totalsRowDxfId="39" dataCellStyle="Normal 41"/>
-    <tableColumn id="5" xr3:uid="{9801F608-BB2B-4D0C-8971-505EA1A3413E}" name="FACTOR" dataDxfId="36" totalsRowDxfId="37" dataCellStyle="Normal 41">
-      <calculatedColumnFormula xml:space="preserve"> 1</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="6" xr3:uid="{7038F064-05D1-447F-9CF9-7F184E21A8D8}" name="CANTIDAD" dataDxfId="34" totalsRowDxfId="35" dataCellStyle="Normal 41"/>
-    <tableColumn id="7" xr3:uid="{F2AC5DE0-E7AE-440D-8B08-09F19B7EA380}" name="PRECIO" dataDxfId="32" totalsRowDxfId="33" dataCellStyle="Normal 41"/>
-    <tableColumn id="8" xr3:uid="{6F05E439-9D18-41B1-94E6-B38F9532F857}" name="TOTAL" totalsRowFunction="custom" dataDxfId="30" totalsRowDxfId="31" dataCellStyle="Normal 12 3">
-      <calculatedColumnFormula>Tabla5[[#This Row],[CANTIDAD]]*Tabla5[[#This Row],[PRECIO]]*Tabla5[[#This Row],[FACTOR]]</calculatedColumnFormula>
-      <totalsRowFormula>SUM(Tabla5[TOTAL])</totalsRowFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="S5S Blue" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="INSUMOS"/>
+      <sheetName val="BÁSICOS"/>
+      <sheetName val="APU"/>
+      <sheetName val="PRESUPUESTO"/>
+      <sheetName val="LISTA_BÁSICOS"/>
+      <sheetName val="LISTA_APU"/>
+      <sheetName val="MATERIALES"/>
+      <sheetName val="Bugs"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2250,7 +2893,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15972434-AFA7-4552-A5DE-6EDC07CBECCE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322D7FD8-8E1E-44D1-982F-D85C01143FD7}">
   <sheetPr codeName="Hoja2">
     <tabColor rgb="FF00AC56"/>
     <pageSetUpPr fitToPage="1"/>
@@ -2488,18 +3131,30 @@
         <v>14</v>
       </c>
       <c r="D5" s="12">
-        <v>10</v>
+        <v>2694</v>
       </c>
       <c r="E5" s="19"/>
-      <c r="G5" s="10"/>
+      <c r="G5" s="10" t="s">
+        <v>15</v>
+      </c>
       <c r="H5" s="10"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="12"/>
+      <c r="I5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="12">
+        <v>100000</v>
+      </c>
       <c r="K5" s="19"/>
-      <c r="M5" s="10"/>
+      <c r="M5" s="10" t="s">
+        <v>17</v>
+      </c>
       <c r="N5" s="10"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="12"/>
+      <c r="O5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="P5" s="12">
+        <v>21793</v>
+      </c>
       <c r="Q5" s="19"/>
       <c r="S5" s="15"/>
       <c r="T5" s="15"/>
@@ -2524,20 +3179,26 @@
     </row>
     <row r="6" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D6" s="12">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E6" s="13"/>
-      <c r="G6" s="10"/>
+      <c r="G6" s="10" t="s">
+        <v>21</v>
+      </c>
       <c r="H6" s="10"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="14"/>
+      <c r="I6" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="12">
+        <v>110215</v>
+      </c>
       <c r="K6" s="13"/>
       <c r="M6" s="15"/>
       <c r="N6" s="15"/>
@@ -2566,11 +3227,17 @@
       <c r="AO6" s="18"/>
     </row>
     <row r="7" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="10"/>
+      <c r="A7" s="10" t="s">
+        <v>23</v>
+      </c>
       <c r="B7" s="10"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="13"/>
+      <c r="C7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="12">
+        <v>7400</v>
+      </c>
+      <c r="E7" s="19"/>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
       <c r="I7" s="11"/>
@@ -2603,10 +3270,16 @@
       <c r="AO7" s="18"/>
     </row>
     <row r="8" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="10"/>
+      <c r="A8" s="10" t="s">
+        <v>24</v>
+      </c>
       <c r="B8" s="10"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="12"/>
+      <c r="C8" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="12">
+        <v>285000</v>
+      </c>
       <c r="E8" s="13"/>
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
@@ -2640,10 +3313,16 @@
       <c r="AO8" s="18"/>
     </row>
     <row r="9" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="10"/>
+      <c r="A9" s="10" t="s">
+        <v>26</v>
+      </c>
       <c r="B9" s="10"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="12"/>
+      <c r="C9" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="12">
+        <v>486</v>
+      </c>
       <c r="E9" s="13"/>
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
@@ -2677,10 +3356,16 @@
       <c r="AO9" s="18"/>
     </row>
     <row r="10" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="10"/>
+      <c r="A10" s="10" t="s">
+        <v>27</v>
+      </c>
       <c r="B10" s="10"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="12"/>
+      <c r="C10" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="12">
+        <v>72500</v>
+      </c>
       <c r="E10" s="13"/>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
@@ -2714,6 +3399,7 @@
       <c r="AO10" s="18"/>
     </row>
     <row r="11" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E11" s="13"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
       <c r="I11" s="11"/>
@@ -2745,6 +3431,34 @@
       <c r="AN11" s="17"/>
       <c r="AO11" s="18"/>
     </row>
+    <row r="12" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="13"/>
+    </row>
+    <row r="13" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="13"/>
+    </row>
+    <row r="14" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="13"/>
+    </row>
+    <row r="15" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="13"/>
+    </row>
     <row r="22" spans="12:39" x14ac:dyDescent="0.3">
       <c r="O22" s="20"/>
     </row>
@@ -3404,42 +4118,32 @@
     <brk id="35" max="1048575" man="1"/>
     <brk id="41" max="1048575" man="1"/>
   </colBreaks>
-  <tableParts count="7">
-    <tablePart r:id="rId2"/>
-    <tablePart r:id="rId3"/>
-    <tablePart r:id="rId4"/>
-    <tablePart r:id="rId5"/>
-    <tablePart r:id="rId6"/>
-    <tablePart r:id="rId7"/>
-    <tablePart r:id="rId8"/>
-  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D27C1B0B-28F4-4EA0-8962-CC703644D878}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA47168D-6188-4F80-BFD0-34DDC2DF7BD1}">
   <sheetPr codeName="Hoja3">
     <tabColor rgb="FF0088CC"/>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40.77734375" customWidth="1"/>
-    <col min="4" max="4" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.21875" style="21" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.44140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="8.77734375" style="21" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="1.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -3455,10 +4159,10 @@
     </row>
     <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="23" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C3" s="25"/>
       <c r="D3" s="25"/>
@@ -3466,184 +4170,602 @@
       <c r="F3" s="25"/>
       <c r="G3" s="26"/>
       <c r="H3" s="27" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="18" t="s">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="18"/>
+      <c r="D5" s="3"/>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="D6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5">
-        <f>VLOOKUP(Tabla3[[#This Row],[DESCRIPCIÓN]],T_mat[[DESCRIPCIÓN]:[PRECIO]],2,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="3" t="str">
-        <f>VLOOKUP(Tabla3[[#This Row],[DESCRIPCIÓN]],T_mat[[DESCRIPCIÓN]:[PRECIO]],3,FALSE)</f>
-        <v>lt</v>
-      </c>
-      <c r="E5">
-        <f>1</f>
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4">
-        <f>VLOOKUP(Tabla3[[#This Row],[DESCRIPCIÓN]],T_mat[[DESCRIPCIÓN]:[PRECIO]],4,FALSE)</f>
-        <v>10</v>
-      </c>
-      <c r="H5" s="4">
-        <f>Tabla3[[#This Row],[CANTIDAD]]*Tabla3[[#This Row],[PRECIO]]*Tabla3[[#This Row],[FACTOR]]</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" t="e">
-        <f>VLOOKUP(Tabla3[[#This Row],[DESCRIPCIÓN]],T_mat[[DESCRIPCIÓN]:[PRECIO]],2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="3" t="e">
-        <f>VLOOKUP(Tabla3[[#This Row],[DESCRIPCIÓN]],T_mat[[DESCRIPCIÓN]:[PRECIO]],3,FALSE)</f>
-        <v>#N/A</v>
-      </c>
       <c r="E6">
-        <f>1</f>
         <v>1</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
-      <c r="G6" s="4" t="e">
-        <f>VLOOKUP(Tabla3[[#This Row],[DESCRIPCIÓN]],T_mat[[DESCRIPCIÓN]:[PRECIO]],4,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H6" s="4" t="e">
-        <f>Tabla3[[#This Row],[CANTIDAD]]*Tabla3[[#This Row],[PRECIO]]*Tabla3[[#This Row],[FACTOR]]</f>
-        <v>#N/A</v>
+      <c r="G6" s="4">
+        <v>285000</v>
+      </c>
+      <c r="H6" s="4">
+        <v>570000</v>
       </c>
     </row>
     <row r="7" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="18"/>
+      <c r="D7" s="3"/>
+      <c r="E7">
         <v>1</v>
       </c>
-      <c r="B7">
-        <f>VLOOKUP(Tabla3[[#This Row],[DESCRIPCIÓN]],T_mat[[DESCRIPCIÓN]:[PRECIO]],2,FALSE)</f>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4">
         <v>0</v>
       </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="3" t="str">
-        <f>VLOOKUP(Tabla3[[#This Row],[DESCRIPCIÓN]],T_mat[[DESCRIPCIÓN]:[PRECIO]],3,FALSE)</f>
-        <v>m3</v>
-      </c>
-      <c r="E7">
-        <f>1</f>
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7" s="4">
-        <f>VLOOKUP(Tabla3[[#This Row],[DESCRIPCIÓN]],T_mat[[DESCRIPCIÓN]:[PRECIO]],4,FALSE)</f>
-        <v>30</v>
-      </c>
-      <c r="H7" s="4">
-        <f>Tabla3[[#This Row],[CANTIDAD]]*Tabla3[[#This Row],[PRECIO]]*Tabla3[[#This Row],[FACTOR]]</f>
-        <v>90</v>
-      </c>
     </row>
     <row r="8" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="18"/>
       <c r="D8" s="3"/>
       <c r="E8">
-        <f>1</f>
         <v>1</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4">
-        <f>Tabla3[[#This Row],[CANTIDAD]]*Tabla3[[#This Row],[PRECIO]]*Tabla3[[#This Row],[FACTOR]]</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="18"/>
       <c r="D9" s="3"/>
       <c r="E9">
-        <f>1</f>
         <v>1</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4">
-        <f>Tabla3[[#This Row],[CANTIDAD]]*Tabla3[[#This Row],[PRECIO]]*Tabla3[[#This Row],[FACTOR]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
-        <v>27</v>
+    <row r="10" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="18"/>
+      <c r="D10" s="3"/>
+      <c r="E10">
+        <v>1</v>
       </c>
       <c r="G10" s="4"/>
-      <c r="H10" s="17" t="e">
-        <f>SUM(Tabla3[TOTAL])</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G11"/>
-      <c r="H11"/>
+      <c r="H10" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D11" s="3"/>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G12"/>
-      <c r="H12"/>
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4">
+        <v>570000</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G13"/>
       <c r="H13"/>
     </row>
+    <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G14"/>
+      <c r="H14"/>
+    </row>
+    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="18"/>
+      <c r="D17" s="3"/>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18" s="4">
+        <v>285000</v>
+      </c>
+      <c r="H18" s="4">
+        <v>570000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="18"/>
+      <c r="D19" s="3"/>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D20" s="3"/>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D21" s="3"/>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4">
+        <v>570000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G23"/>
+      <c r="H23"/>
+    </row>
+    <row r="24" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G24"/>
+      <c r="H24"/>
+    </row>
+    <row r="25" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" t="s">
+        <v>33</v>
+      </c>
+      <c r="F26" t="s">
+        <v>34</v>
+      </c>
+      <c r="G26" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27" s="4">
+        <v>285000</v>
+      </c>
+      <c r="H27" s="4">
+        <v>570000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="18"/>
+      <c r="D28" s="3"/>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D29" s="3"/>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D30" s="3"/>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>36</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4">
+        <v>570000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G32"/>
+      <c r="H32"/>
+    </row>
+    <row r="33" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G33"/>
+      <c r="H33"/>
+    </row>
+    <row r="34" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G34"/>
+      <c r="H34"/>
+    </row>
+    <row r="35" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G35"/>
+      <c r="H35"/>
+    </row>
+    <row r="36" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G36"/>
+      <c r="H36"/>
+    </row>
+    <row r="37" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G37"/>
+      <c r="H37"/>
+    </row>
+    <row r="38" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G38"/>
+      <c r="H38"/>
+    </row>
+    <row r="39" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G39"/>
+      <c r="H39"/>
+    </row>
+    <row r="40" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G40"/>
+      <c r="H40"/>
+    </row>
+    <row r="41" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G41"/>
+      <c r="H41"/>
+    </row>
+    <row r="42" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G42"/>
+      <c r="H42"/>
+    </row>
+    <row r="43" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G43"/>
+      <c r="H43"/>
+    </row>
+    <row r="44" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G44"/>
+      <c r="H44"/>
+    </row>
+    <row r="45" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G45"/>
+      <c r="H45"/>
+    </row>
+    <row r="46" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G46"/>
+      <c r="H46"/>
+    </row>
+    <row r="47" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G47"/>
+      <c r="H47"/>
+    </row>
+    <row r="48" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G48"/>
+      <c r="H48"/>
+    </row>
+    <row r="49" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G49"/>
+      <c r="H49"/>
+    </row>
+    <row r="50" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G50"/>
+      <c r="H50"/>
+    </row>
+    <row r="51" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G51"/>
+      <c r="H51"/>
+    </row>
+    <row r="52" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G52"/>
+      <c r="H52"/>
+    </row>
+    <row r="53" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G53"/>
+      <c r="H53"/>
+    </row>
+    <row r="54" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G54"/>
+      <c r="H54"/>
+    </row>
+    <row r="55" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G55"/>
+      <c r="H55"/>
+    </row>
+    <row r="56" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G56"/>
+      <c r="H56"/>
+    </row>
+    <row r="57" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G57"/>
+      <c r="H57"/>
+    </row>
+    <row r="58" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G58"/>
+      <c r="H58"/>
+    </row>
+    <row r="59" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G59"/>
+      <c r="H59"/>
+    </row>
+    <row r="60" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G60"/>
+      <c r="H60"/>
+    </row>
+    <row r="61" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G61"/>
+      <c r="H61"/>
+    </row>
+    <row r="62" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G62"/>
+      <c r="H62"/>
+    </row>
+    <row r="63" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G63"/>
+      <c r="H63"/>
+    </row>
+    <row r="64" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G64"/>
+      <c r="H64"/>
+    </row>
+    <row r="65" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G65"/>
+      <c r="H65"/>
+    </row>
+    <row r="66" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G66"/>
+      <c r="H66"/>
+    </row>
+    <row r="67" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G67"/>
+      <c r="H67"/>
+    </row>
+    <row r="68" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G68"/>
+      <c r="H68"/>
+    </row>
+    <row r="69" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G69"/>
+      <c r="H69"/>
+    </row>
+    <row r="70" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G70"/>
+      <c r="H70"/>
+    </row>
+    <row r="71" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G71"/>
+      <c r="H71"/>
+    </row>
+    <row r="72" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G72"/>
+      <c r="H72"/>
+    </row>
+    <row r="73" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G73"/>
+      <c r="H73"/>
+    </row>
+    <row r="74" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G74"/>
+      <c r="H74"/>
+    </row>
+    <row r="75" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G75"/>
+      <c r="H75"/>
+    </row>
+    <row r="76" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G76"/>
+      <c r="H76"/>
+    </row>
+    <row r="77" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G77"/>
+      <c r="H77"/>
+    </row>
+    <row r="78" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G78"/>
+      <c r="H78"/>
+    </row>
+    <row r="79" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G79"/>
+      <c r="H79"/>
+    </row>
+    <row r="80" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G80"/>
+      <c r="H80"/>
+    </row>
+    <row r="81" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G81"/>
+      <c r="H81"/>
+    </row>
+    <row r="82" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G82"/>
+      <c r="H82"/>
+    </row>
+    <row r="83" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G83"/>
+      <c r="H83"/>
+    </row>
+    <row r="84" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G84"/>
+      <c r="H84"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B25:G25"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C7" xr:uid="{B87816EC-0F5F-4645-8EDC-1D86B84BC2B1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C10 C18 C27" xr:uid="{B9BA5E79-F926-4EBC-B505-333C66388B97}">
       <formula1>MATERIALES</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A5:A9" xr:uid="{F9D8B241-7286-4625-B83A-20116CCC6A95}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A17:A21 A27:A30 A5:A11" xr:uid="{4A60A9F4-DA6C-4095-8033-16A88A866A88}">
       <formula1>"MATERIALES,EQUIPOS,MANO DE OBRA,TRANSPORTE,SUBCONTRATOS,ACTIVIDADES,OTROS"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3652,36 +4774,33 @@
   <colBreaks count="1" manualBreakCount="1">
     <brk id="8" max="1048575" man="1"/>
   </colBreaks>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F5146F1-594D-421F-B44E-6C60963A46D0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{829C927A-5519-4C3B-8021-B5C81272F754}">
   <sheetPr codeName="Hoja7">
     <tabColor rgb="FF00AC56"/>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40.77734375" customWidth="1"/>
-    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8" style="21" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.77734375" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.77734375" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" style="21" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="1.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -3703,10 +4822,10 @@
     </row>
     <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="32" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C3" s="34"/>
       <c r="D3" s="34"/>
@@ -3714,167 +4833,518 @@
       <c r="F3" s="34"/>
       <c r="G3" s="35"/>
       <c r="H3" s="36" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5" s="4">
+        <v>72500</v>
+      </c>
+      <c r="H5" s="4">
+        <v>145000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D6" s="3"/>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="37" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4"/>
-    </row>
-    <row r="5" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="28">
-        <f xml:space="preserve"> 1</f>
+      <c r="E7">
         <v>1</v>
       </c>
-      <c r="E5" s="28">
+      <c r="F7">
         <v>2</v>
       </c>
-      <c r="F5" s="4">
-        <v>140</v>
-      </c>
-      <c r="G5" s="41">
-        <f>Tabla5[[#This Row],[CANTIDAD]]*Tabla5[[#This Row],[PRECIO]]*Tabla5[[#This Row],[FACTOR]]</f>
-        <v>280</v>
-      </c>
-      <c r="H5"/>
-    </row>
-    <row r="6" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="28" t="s">
+      <c r="G7" s="4">
+        <v>110215</v>
+      </c>
+      <c r="H7" s="4">
+        <v>220430</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D8" s="3"/>
+      <c r="E8">
         <v>1</v>
       </c>
-      <c r="B6">
+      <c r="G8" s="4"/>
+      <c r="H8" s="4">
         <v>0</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="28">
-        <f xml:space="preserve"> 1</f>
+    </row>
+    <row r="9" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D9" s="3"/>
+      <c r="E9">
         <v>1</v>
       </c>
-      <c r="E6" s="28">
-        <v>20</v>
-      </c>
-      <c r="F6" s="4">
-        <v>20</v>
-      </c>
-      <c r="G6" s="41">
-        <f>Tabla5[[#This Row],[CANTIDAD]]*Tabla5[[#This Row],[PRECIO]]*Tabla5[[#This Row],[FACTOR]]</f>
-        <v>400</v>
-      </c>
-      <c r="H6"/>
-    </row>
-    <row r="7" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="28"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="28">
-        <f xml:space="preserve"> 1</f>
-        <v>1</v>
-      </c>
-      <c r="E7" s="28"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="41">
-        <f>Tabla5[[#This Row],[CANTIDAD]]*Tabla5[[#This Row],[PRECIO]]*Tabla5[[#This Row],[FACTOR]]</f>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4">
         <v>0</v>
       </c>
-      <c r="H7"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="17">
-        <f>SUM(Tabla5[TOTAL])</f>
-        <v>680</v>
-      </c>
-      <c r="H8"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="28"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="31"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="28"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="31"/>
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4">
+        <v>365430</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G11"/>
       <c r="H11"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="28"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="31"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="28"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="31"/>
+    <row r="12" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G12"/>
+      <c r="H12"/>
+    </row>
+    <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="41" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>4</v>
+      </c>
+      <c r="G15" s="4">
+        <v>570000</v>
+      </c>
+      <c r="H15" s="4">
+        <v>2280000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+      <c r="G16" s="4">
+        <v>570000</v>
+      </c>
+      <c r="H16" s="4">
+        <v>2850000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D17" s="3"/>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D18" s="3"/>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="17">
+        <v>5130000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G20"/>
+      <c r="H20"/>
+    </row>
+    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G21"/>
+      <c r="H21"/>
+    </row>
+    <row r="22" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="41" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H23" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>4</v>
+      </c>
+      <c r="G24" s="4">
+        <v>570000</v>
+      </c>
+      <c r="H24" s="4">
+        <v>2280000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>5</v>
+      </c>
+      <c r="G25" s="4">
+        <v>570000</v>
+      </c>
+      <c r="H25" s="4">
+        <v>2850000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D26" s="3"/>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D27" s="3"/>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="17">
+        <v>5130000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G29"/>
+      <c r="H29"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G30"/>
+      <c r="H30"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G31"/>
+      <c r="H31"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G32"/>
+      <c r="H32"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G33"/>
+      <c r="H33"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G34"/>
+      <c r="H34"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G35"/>
+      <c r="H35"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G36"/>
+      <c r="H36"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G37"/>
+      <c r="H37"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G38"/>
+      <c r="H38"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G39"/>
+      <c r="H39"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G40"/>
+      <c r="H40"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G41"/>
+      <c r="H41"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G42"/>
+      <c r="H42"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G43"/>
+      <c r="H43"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G44"/>
+      <c r="H44"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G45"/>
+      <c r="H45"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="28"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="31"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="28"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="31"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G48"/>
+      <c r="H48"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="28"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="28"/>
+      <c r="H49" s="31"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="28"/>
+      <c r="B50" s="29"/>
+      <c r="C50" s="30"/>
+      <c r="D50" s="30"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="28"/>
+      <c r="G50" s="28"/>
+      <c r="H50" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B22:G22"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A5:A7" xr:uid="{B8F3CF3A-DFA8-4177-B9FD-B03FB10A4595}">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C15:C17 C24:C25" xr:uid="{706CFD18-C37F-4842-9DA2-484DAEB1A124}">
+      <formula1>BÁSICOS</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5" xr:uid="{9EB12D10-CE7C-43B6-9CFA-B5214C8BE64C}">
+      <formula1>MATERIALES</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6:C7" xr:uid="{ED1364DA-51A5-44AD-ABB4-060E506A2BCC}">
+      <formula1>EQUIPOS</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A5:A9 A15:A18 A24:A27" xr:uid="{C4966E95-138A-49D5-A325-9AB1A3BF8E64}">
       <formula1>"MATERIALES,EQUIPOS,MANO DE OBRA,TRANSPORTE,SUBCONTRATOS,ACTIVIDADES,OTROS,APU BÁSICOS"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3883,299 +5353,782 @@
   <colBreaks count="1" manualBreakCount="1">
     <brk id="8" max="1048575" man="1"/>
   </colBreaks>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCCBCF94-6A70-43BC-8AE0-66F56202A414}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88423E83-4F83-4993-A86F-08C789C4864F}">
   <sheetPr codeName="Hoja1">
     <tabColor rgb="FF0088CC"/>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.44140625" style="49" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" style="51" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.77734375" style="52" customWidth="1"/>
-    <col min="4" max="4" width="23" style="51" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" style="53" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.21875" style="53" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" style="53" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" style="53" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="1.33203125" style="49" customWidth="1"/>
-    <col min="10" max="16384" width="11.44140625" style="49"/>
+    <col min="1" max="1" width="1.44140625" style="43" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" style="44" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.77734375" style="45" customWidth="1"/>
+    <col min="4" max="4" width="23" style="44" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.88671875" style="46" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.21875" style="46" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" style="46" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.88671875" style="46" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="1.33203125" style="43" customWidth="1"/>
+    <col min="10" max="16384" width="11.44140625" style="43"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
+      <c r="B1" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
     </row>
     <row r="2" spans="2:8" ht="15.6" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="50" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="15.6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="52" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="53" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="45" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="46">
+        <v>1</v>
+      </c>
+      <c r="F5" s="46">
+        <v>4</v>
+      </c>
+      <c r="G5" s="46">
+        <v>5130000</v>
+      </c>
+      <c r="H5" s="46">
+        <v>20520000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="46">
+        <v>1</v>
+      </c>
+      <c r="F6" s="46">
+        <v>2</v>
+      </c>
+      <c r="G6" s="46">
+        <v>365430</v>
+      </c>
+      <c r="H6" s="46">
+        <v>730860</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="45" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="46">
+        <v>1</v>
+      </c>
+      <c r="F7" s="46">
+        <v>1</v>
+      </c>
+      <c r="G7" s="46">
+        <v>5130000</v>
+      </c>
+      <c r="H7" s="46">
+        <v>5130000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="46">
+        <v>1</v>
+      </c>
+      <c r="G8" s="46">
+        <v>5130000</v>
+      </c>
+      <c r="H8" s="46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="45" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="46">
+        <v>1</v>
+      </c>
+      <c r="F9" s="46">
+        <v>5</v>
+      </c>
+      <c r="G9" s="46">
+        <v>5130000</v>
+      </c>
+      <c r="H9" s="46">
+        <v>25650000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="46">
+        <v>1</v>
+      </c>
+      <c r="F10" s="46">
+        <v>5</v>
+      </c>
+      <c r="G10" s="46">
+        <v>365430</v>
+      </c>
+      <c r="H10" s="46">
+        <v>1827150</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="46">
+        <v>1</v>
+      </c>
+      <c r="F11" s="46">
+        <v>1</v>
+      </c>
+      <c r="G11" s="46">
+        <v>365430</v>
+      </c>
+      <c r="H11" s="46">
+        <v>365430</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="E12" s="46">
+        <v>1</v>
+      </c>
+      <c r="H12" s="46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B13" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" s="53">
+        <v>54223440</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" ht="15.6" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="2:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="50" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="15.6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="52" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="H17" s="53" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="46">
+        <v>1</v>
+      </c>
+      <c r="F18" s="46">
+        <v>3</v>
+      </c>
+      <c r="G18" s="46">
+        <v>365430</v>
+      </c>
+      <c r="H18" s="46">
+        <v>1096290</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="46">
+        <v>1</v>
+      </c>
+      <c r="F19" s="46">
+        <v>3</v>
+      </c>
+      <c r="G19" s="46">
+        <v>365430</v>
+      </c>
+      <c r="H19" s="46">
+        <v>1096290</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="45" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="46">
+        <v>1</v>
+      </c>
+      <c r="F20" s="46">
+        <v>2</v>
+      </c>
+      <c r="G20" s="46">
+        <v>5130000</v>
+      </c>
+      <c r="H20" s="46">
+        <v>10260000</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="E21" s="46">
+        <v>1</v>
+      </c>
+      <c r="H21" s="46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="E22" s="46">
+        <v>1</v>
+      </c>
+      <c r="H22" s="46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="45" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="46">
+        <v>1</v>
+      </c>
+      <c r="F23" s="46">
+        <v>5</v>
+      </c>
+      <c r="G23" s="46">
+        <v>5130000</v>
+      </c>
+      <c r="H23" s="46">
+        <v>25650000</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" s="46">
+        <v>1</v>
+      </c>
+      <c r="F24" s="46">
+        <v>1</v>
+      </c>
+      <c r="G24" s="46">
+        <v>365430</v>
+      </c>
+      <c r="H24" s="46">
+        <v>365430</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="45" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="46">
+        <v>1</v>
+      </c>
+      <c r="F25" s="46">
+        <v>1</v>
+      </c>
+      <c r="G25" s="46">
+        <v>5130000</v>
+      </c>
+      <c r="H25" s="46">
+        <v>5130000</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="E26" s="46">
+        <v>1</v>
+      </c>
+      <c r="H26" s="46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B27" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="H27" s="53">
+        <v>43598010</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" ht="15.6" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="2:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" s="48"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="48"/>
+      <c r="G30" s="49"/>
+      <c r="H30" s="50" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" ht="15.6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="52" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F31" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="G31" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="H31" s="53" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32" s="46">
+        <v>1</v>
+      </c>
+      <c r="F32" s="46">
+        <v>3</v>
+      </c>
+      <c r="G32" s="46">
+        <v>365430</v>
+      </c>
+      <c r="H32" s="46">
+        <v>1096290</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33" s="46">
+        <v>1</v>
+      </c>
+      <c r="F33" s="46">
+        <v>232</v>
+      </c>
+      <c r="G33" s="46">
+        <v>365430</v>
+      </c>
+      <c r="H33" s="46">
+        <v>84779760</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" s="45" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" s="46">
+        <v>1</v>
+      </c>
+      <c r="F34" s="46">
         <v>32</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="57" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" ht="15.6" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="59" t="s">
+      <c r="G34" s="46">
+        <v>5130000</v>
+      </c>
+      <c r="H34" s="46">
+        <v>164160000</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35" s="46">
+        <v>1</v>
+      </c>
+      <c r="F35" s="46">
+        <v>21</v>
+      </c>
+      <c r="G35" s="46">
+        <v>365430</v>
+      </c>
+      <c r="H35" s="46">
+        <v>7674030</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="E36" s="46">
+        <v>1</v>
+      </c>
+      <c r="H36" s="46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B37" s="54" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="55"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="53">
+        <v>257710080</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F40" s="51"/>
+      <c r="G40" s="51"/>
+      <c r="H40" s="53"/>
+    </row>
+    <row r="41" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B41" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="D41" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="E41" s="53" t="s">
+        <v>48</v>
+      </c>
+      <c r="F41" s="44"/>
+      <c r="G41" s="44"/>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B42" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="D42" s="57">
+        <v>0.15251373063874252</v>
+      </c>
+      <c r="E42" s="46">
+        <v>54223440</v>
+      </c>
+      <c r="F42" s="44"/>
+      <c r="G42" s="44"/>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B43" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43" s="45" t="s">
+        <v>45</v>
+      </c>
+      <c r="D43" s="57">
+        <v>0.12262768930789344</v>
+      </c>
+      <c r="E43" s="46">
+        <v>43598010</v>
+      </c>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B44" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44" s="45" t="s">
+        <v>46</v>
+      </c>
+      <c r="D44" s="57">
+        <v>0.72485858005336401</v>
+      </c>
+      <c r="E44" s="46">
+        <v>257710080</v>
+      </c>
+      <c r="F44" s="44"/>
+      <c r="G44" s="44"/>
+    </row>
+    <row r="47" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B47" s="58"/>
+      <c r="C47" s="59"/>
+      <c r="D47" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="E47" s="61">
+        <v>355531530</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B48" s="62" t="s">
+        <v>50</v>
+      </c>
+      <c r="C48" s="62"/>
+      <c r="D48" s="62"/>
+      <c r="E48" s="62"/>
+    </row>
+    <row r="50" spans="3:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C50" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="60" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" s="60" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="51" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="53">
-        <v>1</v>
-      </c>
-      <c r="F5" s="53">
-        <v>23</v>
-      </c>
-      <c r="G5" s="53">
-        <v>680</v>
-      </c>
-      <c r="H5" s="53">
-        <f>Tabla7[[#This Row],[FACTOR]]*Tabla7[[#This Row],[CANTIDAD]]*Tabla7[[#This Row],[COSTO]]</f>
-        <v>15640</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="E6" s="53">
-        <v>1</v>
-      </c>
-      <c r="H6" s="53">
-        <f>Tabla7[[#This Row],[FACTOR]]*Tabla7[[#This Row],[CANTIDAD]]*Tabla7[[#This Row],[COSTO]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="E7" s="53">
-        <v>1</v>
-      </c>
-      <c r="H7" s="53">
-        <f>Tabla7[[#This Row],[FACTOR]]*Tabla7[[#This Row],[CANTIDAD]]*Tabla7[[#This Row],[COSTO]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="E8" s="53">
-        <v>1</v>
-      </c>
-      <c r="H8" s="53">
-        <f>Tabla7[[#This Row],[FACTOR]]*Tabla7[[#This Row],[CANTIDAD]]*Tabla7[[#This Row],[COSTO]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="E9" s="53">
-        <v>1</v>
-      </c>
-      <c r="H9" s="53">
-        <f>Tabla7[[#This Row],[FACTOR]]*Tabla7[[#This Row],[CANTIDAD]]*Tabla7[[#This Row],[COSTO]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="58" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="60">
-        <f>SUM(Tabla7[TOTAL])</f>
-        <v>15640</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="60"/>
-    </row>
-    <row r="14" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B14" s="58" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="59" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="58" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="60" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="51" t="str">
-        <f>$H$3</f>
-        <v>CÓD</v>
-      </c>
-      <c r="C15" s="52" t="str">
-        <f>$B$3</f>
-        <v>CAPÍTULO</v>
-      </c>
-      <c r="D15" s="51">
-        <f>(E15)/(E18)</f>
-        <v>1</v>
-      </c>
-      <c r="E15" s="53">
-        <f>$H$10</f>
-        <v>15640</v>
-      </c>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="F16" s="51"/>
-      <c r="G16" s="51"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F17" s="51"/>
-      <c r="G17" s="51"/>
-    </row>
-    <row r="18" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B18" s="61"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="63" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="64">
-        <f>SUM(E15:E17)</f>
-        <v>15640</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C21" s="59" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="58" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="60" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C22" s="52" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" s="65">
-        <v>0</v>
-      </c>
-      <c r="E22" s="51">
-        <f>Tabla13[[#This Row],[PORCENTAJE]]*E18</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C23" s="52" t="s">
-        <v>38</v>
-      </c>
-      <c r="D23" s="65">
-        <v>0</v>
-      </c>
-      <c r="E23" s="51">
-        <f>Tabla13[[#This Row],[PORCENTAJE]]*E18</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C24" s="52" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" s="65">
-        <v>0</v>
-      </c>
-      <c r="E24" s="51">
-        <f>Tabla13[[#This Row],[PORCENTAJE]]*E18</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C25" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" s="65">
-        <v>0</v>
-      </c>
-      <c r="E25" s="51">
-        <f>Tabla13[[#This Row],[PORCENTAJE]]*E24</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D26" s="66" t="s">
-        <v>41</v>
-      </c>
-      <c r="E26" s="58">
-        <f>SUM(E22:E25)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E27" s="51"/>
-    </row>
-    <row r="28" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D28" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E28" s="58">
-        <f>E18+E26</f>
-        <v>15640</v>
+      <c r="D50" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="E50" s="53" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C51" s="45" t="s">
+        <v>51</v>
+      </c>
+      <c r="D51" s="63">
+        <v>0.05</v>
+      </c>
+      <c r="E51" s="64">
+        <v>17776576.5</v>
+      </c>
+    </row>
+    <row r="52" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C52" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="D52" s="63">
+        <v>0.05</v>
+      </c>
+      <c r="E52" s="64">
+        <v>17776576.5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C53" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="D53" s="63">
+        <v>0.1</v>
+      </c>
+      <c r="E53" s="64">
+        <v>35553153</v>
+      </c>
+    </row>
+    <row r="54" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C54" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="D54" s="63">
+        <v>0.19</v>
+      </c>
+      <c r="E54" s="64">
+        <v>6755099.0700000003</v>
+      </c>
+    </row>
+    <row r="55" spans="3:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D55" s="65" t="s">
+        <v>55</v>
+      </c>
+      <c r="E55" s="66">
+        <v>77861405.069999993</v>
+      </c>
+    </row>
+    <row r="56" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E56" s="64"/>
+    </row>
+    <row r="57" spans="3:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D57" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="E57" s="66">
+        <v>433392935.06999999</v>
       </c>
     </row>
   </sheetData>
   <dataConsolidate/>
-  <mergeCells count="2">
+  <mergeCells count="5">
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="B48:E48"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C9" xr:uid="{0993DE00-A823-4F30-8C3E-25470E73C4C6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C18:C26 C32:C36 C5:C12" xr:uid="{D03F6125-4C22-4499-B5A9-9DB1B1F414AD}">
       <formula1>BD_APUS</formula1>
     </dataValidation>
   </dataValidations>
@@ -4184,10 +6137,6 @@
   <colBreaks count="1" manualBreakCount="1">
     <brk id="8" max="1048575" man="1"/>
   </colBreaks>
-  <tableParts count="3">
-    <tablePart r:id="rId2"/>
-    <tablePart r:id="rId3"/>
-    <tablePart r:id="rId4"/>
-  </tableParts>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>